--- a/docs/downloads/16082026Tduh Developer Project Sales Status 13.xlsx
+++ b/docs/downloads/16082026Tduh Developer Project Sales Status 13.xlsx
@@ -485,7 +485,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:AZ17"/>
+  <dimension ref="A2:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -3094,6 +3094,76 @@
       <c r="AY17" s="11" t="n"/>
       <c r="AZ17" s="12" t="n"/>
     </row>
+    <row r="18">
+      <c r="A18" s="7" t="n">
+        <v>14</v>
+      </c>
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>BINASTRA COCHRANE</t>
+        </is>
+      </c>
+      <c r="C18" s="7" t="inlineStr">
+        <is>
+          <t>31332-1</t>
+        </is>
+      </c>
+      <c r="D18" s="8" t="inlineStr">
+        <is>
+          <t>BINASTRA SYNERGY SDN. BHD.</t>
+        </is>
+      </c>
+      <c r="E18" s="9" t="n">
+        <v>830</v>
+      </c>
+      <c r="F18" s="9" t="n"/>
+      <c r="G18" s="10" t="n"/>
+      <c r="H18" s="9" t="n"/>
+      <c r="I18" s="9" t="n"/>
+      <c r="J18" s="10" t="n"/>
+      <c r="K18" s="9" t="n"/>
+      <c r="L18" s="9" t="n"/>
+      <c r="M18" s="10" t="n"/>
+      <c r="N18" s="9" t="n"/>
+      <c r="O18" s="9" t="n"/>
+      <c r="P18" s="10" t="n"/>
+      <c r="Q18" s="9" t="n"/>
+      <c r="R18" s="9" t="n"/>
+      <c r="S18" s="10" t="n"/>
+      <c r="T18" s="9" t="n"/>
+      <c r="U18" s="9" t="n"/>
+      <c r="V18" s="10" t="n"/>
+      <c r="W18" s="9" t="n"/>
+      <c r="X18" s="9" t="n"/>
+      <c r="Y18" s="10" t="n"/>
+      <c r="Z18" s="9" t="n"/>
+      <c r="AA18" s="9" t="n"/>
+      <c r="AB18" s="10" t="n"/>
+      <c r="AC18" s="9" t="n"/>
+      <c r="AD18" s="9" t="n"/>
+      <c r="AE18" s="10" t="n"/>
+      <c r="AF18" s="9" t="n"/>
+      <c r="AG18" s="9" t="n"/>
+      <c r="AH18" s="10" t="n"/>
+      <c r="AI18" s="9" t="n"/>
+      <c r="AJ18" s="9" t="n"/>
+      <c r="AK18" s="10" t="n"/>
+      <c r="AL18" s="9" t="n"/>
+      <c r="AM18" s="9" t="n"/>
+      <c r="AN18" s="10" t="n"/>
+      <c r="AO18" s="9" t="n"/>
+      <c r="AP18" s="9" t="n"/>
+      <c r="AQ18" s="10" t="n"/>
+      <c r="AR18" s="9" t="n"/>
+      <c r="AS18" s="9" t="n"/>
+      <c r="AT18" s="10" t="n"/>
+      <c r="AU18" s="9" t="n"/>
+      <c r="AV18" s="9" t="n"/>
+      <c r="AW18" s="10" t="n"/>
+      <c r="AX18" s="11" t="n"/>
+      <c r="AY18" s="11" t="n"/>
+      <c r="AZ18" s="12" t="n"/>
+    </row>
   </sheetData>
   <mergeCells count="16">
     <mergeCell ref="F3:G3"/>
